--- a/data_for_processing/planograms/Кофе_зерновой_растворимый_1.xlsx
+++ b/data_for_processing/planograms/Кофе_зерновой_растворимый_1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.entaeva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\work\ts\!КЭШ-Операторы\!!! ЗАБОРНИКИ\график заявок по складам!\САЯНА\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3927813D-BD31-4A5D-857C-610CA9BB2A9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11700"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24705" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planogramm" sheetId="2" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Кофе EGOISTE Ethiopia Ground Capsules 10капсул*5гр (777) 1*12</t>
   </si>
@@ -33,173 +34,161 @@
     <t>Кофе EGOISTE Peru Ground Capsules 10капсул*5гр (753) 1*12</t>
   </si>
   <si>
+    <t>Кофе JARDIN Анданте 10капс*5гр (539) 1*10 1353-10-1</t>
+  </si>
+  <si>
     <t>Кофе JARDIN Ваниллиа 10капс*5гр (553) 1*10 1355-10-1</t>
   </si>
   <si>
-    <t>Кофе JARDIN Анданте 10капс*5гр (539) 1*10 1353-10-1</t>
-  </si>
-  <si>
-    <t>Кофе LAVAZZA Qualita Oro 100% Арабика зерно 1кг м/у (566) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе LAVAZZA Crema Е Aroma зерно средн обжарки 1кг м/у (441) 1*6</t>
+    <t>Кофе MONARCH Золото Арабики натуральный жареный в зёрнах 800гр (351) 1*6</t>
+  </si>
+  <si>
+    <t>Кофе TODAY Espresso Blend 7 зерно 1000гр м/у (745) 1*4</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Браво Бразилия зерно 1000гр м/у (478) 1*6 1347-06</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Колумбия Супремо зерно 1000гр м/у (050) 1*6 0605-8 (098/050)</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Эфиопия Эйфория зерно 1000гр м/у (461) 1*6 1346-06</t>
+  </si>
+  <si>
+    <t>Кофе JULIUS MEINL Крема Интенсо Тренд Коллекция зерно 1кг м/у (358) 1*6</t>
+  </si>
+  <si>
+    <t>Кофе BARISTA Pro Italiano жареный в зернах 800гр м/у (101) 1*6</t>
+  </si>
+  <si>
+    <t>Кофе BARISTA Pro Bar жареный в зернах 1000гр м/у (256) 1 *6</t>
+  </si>
+  <si>
+    <t>Кофе BARISTA Pro Итальяно зерно 1000гр м/у (477) 1*6</t>
+  </si>
+  <si>
+    <t>Кофе LE SELECT Espresso Crema зерно 1кг м/у (538) 1*10</t>
+  </si>
+  <si>
+    <t>Кофе LE SELECT Nero Italia зерно 1кг м/у (491) 1*10</t>
+  </si>
+  <si>
+    <t>Кофе BUSHIDO Specialty Coffee зерновой (Швейцария) 227гр м/у (275) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе BUSHIDO Sensei зерновой (Швейцария) 227гр м/у (398) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе BUSHIDO Black Katana зерно (Швейцария) 227гр м/у (497) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе EGOISTE Noir зерно 250гр в/у (196) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе EGOISTE Truffle зерно 250гр м/у (391) 1*12</t>
   </si>
   <si>
     <t>Кофе LAVAZZA Qualita Oro 100% Арабика зерно 250гр м/у (511) 1*20</t>
   </si>
   <si>
-    <t>Кофе TODAY Espresso Blend 7 зерно 1000гр м/у (745) 1*4</t>
-  </si>
-  <si>
-    <t>Кофе JULIUS MEINL Крема Интенсо Тренд Коллекция зерно 1кг м/у (358) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе JARDIN Браво Бразилия зерно 1000гр м/у (478) 1*6 1347-06</t>
-  </si>
-  <si>
-    <t>Кофе JARDIN Колумбия Супремо зерно 1000гр м/у (050) 1*6 0605-8 (098/050)</t>
-  </si>
-  <si>
-    <t>Кофе JARDIN Эфиопия Эйфория зерно 1000гр м/у (461) 1*6 1346-06</t>
+    <t>Кофе JARDIN Американо Крема зерно 250гр м/у (527) 1*12 0552-12</t>
   </si>
   <si>
     <t>Кофе JARDIN Кафе Эклер зерно 250гр м/у (416) 1*12 1341-12</t>
   </si>
   <si>
-    <t>Кофе JARDIN Американо Крема зерно 250гр м/у (527) 1*12 0552-12</t>
-  </si>
-  <si>
-    <t>Кофе MONARCH Золото Арабики натуральный жареный в зёрнах 800гр (351) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе MONARCH Золото Арабики натуральный жареный в зернах 200гр (337) 1*9</t>
-  </si>
-  <si>
-    <t>Кофе MONARCH Ориджинал натуральный жареный в зёрнах 230гр м/у (194) 1*9</t>
-  </si>
-  <si>
-    <t>Кофе EGOISTE Noir зерно 250гр в/у (196) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе EGOISTE Truffle зерно 250гр м/у (391) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе ЧЕРНАЯ КАРТА зерно 1000гр м/у (213) 1*6</t>
+    <t>Кофе LEBO Экстра Арабика зерно высш сорт  м/у 250 гр  (753) 1*20</t>
   </si>
   <si>
     <t>Кофе ЧЕРНАЯ КАРТА Crema зерно 200гр м/у (468) 1*12</t>
   </si>
   <si>
-    <t>Кофе BARISTA Pro Bar жареный в зернах 1000гр м/у (256) 1 *6</t>
-  </si>
-  <si>
-    <t>Кофе BARISTA Pro Итальяно зерно 1000гр м/у (477) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе BARISTA Pro Italiano жареный в зернах 800гр м/у (101) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе LE SELECT Espresso Crema зерно 1кг м/у (538) 1*10</t>
-  </si>
-  <si>
-    <t>Кофе ЖОКЕЙ Традиционный зерно 800гр м/у (753) 1*6 1975-06</t>
-  </si>
-  <si>
-    <t>Кофе LE SELECT Nero Italia зерно 1кг м/у (491) 1*10</t>
+    <t>Кофе ЖОКЕЙ Традиционный зерно 400гр  м/у (103) 1*10 0310-10</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Классический зерно 250гр м/у 0246 (465) 1*10 0246-10</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Традиционный зерно 200гр м/у (097) 1*10 0309-24</t>
+  </si>
+  <si>
+    <t>Кофе AROTI Blend №2 зерно 180гр м/у (195/366) 1*10</t>
   </si>
   <si>
     <t>Кофе LE SELECT Extra Aroma зерно 200гр м/у (392/034) 1*9</t>
   </si>
   <si>
+    <t>Кофе LE SELECT Nero Italia зерно 200гр м/у (460/038) 1*9</t>
+  </si>
+  <si>
     <t>Кофе LE SELECT Espresso Crema зерно 200гр м/у (408/010) 1*9</t>
   </si>
   <si>
-    <t>Кофе AROTI Blend №2 зерно 1кг м/у (119) 1*10</t>
-  </si>
-  <si>
-    <t>Кофе AROTI Blend №2 зерно 180гр м/у (195/366) 1*10</t>
-  </si>
-  <si>
-    <t>Кофе LEBO Экстра Арабика зерно высш сорт  м/у 250 гр  (753) 1*20</t>
-  </si>
-  <si>
-    <t>Кофе ЖОКЕЙ Традиционный зерно 400гр  м/у (103) 1*10 0310-10</t>
-  </si>
-  <si>
-    <t>Кофе ЖОКЕЙ Классический зерно 250гр м/у 0246 (465) 1*10 0246-10</t>
-  </si>
-  <si>
-    <t>Кофе BUSHIDO Specialty Coffee зерновой (Швейцария) 227гр м/у (275) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе BUSHIDO Black Katana зерно (Швейцария) 227гр м/у (497) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе BUSHIDO Sensei зерновой (Швейцария) 227гр м/у (398) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе TODAY PureArabica сублим 95гр ст/б (061) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе TODAY Espresso сублим 95гр ст/б (047) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе TODAY Espresso сублимир.м/у 150гр (110) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе TODAY Espresso сублим 75гр м/у (097) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе TODAY PureArabica сублим 75гр м/у (059) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе АРАБИКА сублим М.К.П. 95гр ст/б (803) 1*8</t>
-  </si>
-  <si>
-    <t>Кофе АРАБИКА растворимый с  молотым МКП 95гр ст/б (334) 1*6</t>
-  </si>
-  <si>
-    <t>Kофе АРАБИКА МКП сублим 75гр м/у (519) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе КОЛОМБО М.К.П. 95гр ст/б 1*8</t>
-  </si>
-  <si>
-    <t>Кофе СУАРЕ растворимый сублим 50гр МКП м/у (202) 1*20</t>
-  </si>
-  <si>
-    <t>Кофе BOURBON The original сублим ст/б 100гр (525) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе Черная Карта Exclusive Brasilia сублим 95гр ст/б (399) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе Черная Карта Gold сублим 95гр ст/б (283/337) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе Черная Карта Exclusive Brasilia сублим 75гр м/у (689) 1*12</t>
-  </si>
-  <si>
-    <t>Кофе AMBASSADOR Platinum сублим 95гр ст/б (951) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе MAXIMUS Gold сублим 95гр ст/б (929) 1*6</t>
-  </si>
-  <si>
-    <t>Кофе MAXIMUS Арабика Colombia сублим 70гр м\у (719) 1*40</t>
-  </si>
-  <si>
-    <t>Кофе MAXIMUS Exclusive сублим с доб. молотого 70гр (967) 1*32</t>
-  </si>
-  <si>
-    <t>Кофе MAXIMUS D'ORO сублим 70гр м/у (983) 1*40</t>
+    <t>Кофе BUSHIDO Black Katana молотый (Швейцария) 227гр м/у (510) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе EGOISTE Espresso молотый 250 гр п/п (172) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе LEBO AROMA IRISH CREAM молотый 150гр м/у (177) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе LEBO AROMA TOFFEE CARAMEL молотый 150гр м/у (184) 1*12</t>
+  </si>
+  <si>
+    <t>Кофе LEBO Экстра Арабика молотый для турки м/у 75 гр (224)   1*40</t>
+  </si>
+  <si>
+    <t>Кофе LAVAZZA Qualita Oro 100% Арабика молот 250гр в/у (911) 1*20</t>
+  </si>
+  <si>
+    <t>Кофе LAVAZZA Crema E Gusto Classico молот 250гр в/у (769) 1*20</t>
+  </si>
+  <si>
+    <t>Kофе АРАБИКА МКП молотый 250гр пакет (090) 1*6</t>
+  </si>
+  <si>
+    <t>Кофе COFFEETURCA Turkish Coffee Молотый 100гр м/у (213/031) 1*15</t>
+  </si>
+  <si>
+    <t>Кофе MONARCH Ориджинал жар. молотый 230гр м/у (217) 1*9</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Американо Крема молот 250гр в/у (565) 1*12 0556-12</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN ОРО молот 250гр (476) 1*6 1747-12</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Колумбия Супремо молот 250гр м/у (800) 1*12 0580-12</t>
+  </si>
+  <si>
+    <t>Кофе JARDIN Кафе Эклер молот 250гр в/у (379) 1*12 1337-12</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Для турки молот 100гр м/у (729) 1*24 0772-24</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Традиционный молот 100гр м/у (066) 1*18 0306-18</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Традиционный молот 250гр в/у (059) 1*26 0305-12</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Для чашки молот 225гр (152) 1*12 1815-12</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ Крепкий молот 225гр (083) 1*12 1508-12</t>
+  </si>
+  <si>
+    <t>Кофе ЖОКЕЙ По-восточному молот 250гр в/у (700) 1*12 0270-12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -212,19 +201,34 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -238,8 +242,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FFADD8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -262,21 +290,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,228 +665,364 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="8.7109375" customWidth="1"/>
+    <col min="1" max="14" width="8.7109375" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="B2" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C2" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="E2" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="F2" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="G2" s="8">
+        <v>16</v>
+      </c>
+      <c r="H2" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="I2" s="8">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5">
+        <v>15</v>
+      </c>
+      <c r="F4" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="6" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8">
+        <v>9</v>
+      </c>
+      <c r="C6" s="8">
+        <v>9</v>
+      </c>
+      <c r="D6" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="E6" s="8">
+        <v>9</v>
+      </c>
+      <c r="F6" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="8" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="D8" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7">
+        <v>9</v>
+      </c>
+      <c r="G8" s="7">
+        <v>9</v>
+      </c>
+      <c r="H8" s="10">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="10" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="B10" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="C10" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="D10" s="9">
+        <v>9</v>
+      </c>
+      <c r="E10" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="F10" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="G10" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="H10" s="12">
+        <v>8</v>
+      </c>
+      <c r="I10" s="9">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="E11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="F11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="G11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="H11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="I11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="J11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="K11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="L11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="M11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="N11" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>57</v>
+    </row>
+    <row r="12" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14">
+        <v>10</v>
+      </c>
+      <c r="C12" s="14">
+        <v>11</v>
+      </c>
+      <c r="D12" s="14">
+        <v>10</v>
+      </c>
+      <c r="E12" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="F12" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="G12" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="I12" s="14">
+        <v>8</v>
+      </c>
+      <c r="J12" s="14">
+        <v>6</v>
+      </c>
+      <c r="K12" s="14">
+        <v>8</v>
+      </c>
+      <c r="L12" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="M12" s="14">
+        <v>8</v>
+      </c>
+      <c r="N12" s="14">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>